--- a/Data/EXCEL/Transfer/salemon/202512/6997-salemon-202512.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202512/6997-salemon-202512.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\202512\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WORKSPACES\xls2xlsx\Transfer\202512\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1F0E97BE-64CA-4BFF-800D-08C5CF410F0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{34CC87F4-B04C-47DE-9234-A2C72A9BB41C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8340" yWindow="930" windowWidth="26910" windowHeight="18975" xr2:uid="{0EB35F0E-8B5E-4962-BF0F-F91AA1CB8378}"/>
+    <workbookView xWindow="0" yWindow="1740" windowWidth="17565" windowHeight="11295" xr2:uid="{5EB11A19-FBB1-40C1-BFF0-E5C68CAE8814}"/>
   </bookViews>
   <sheets>
     <sheet name="6997-salemon-202512" sheetId="2" r:id="rId1"/>
@@ -857,13 +857,13 @@
     <xf numFmtId="0" fontId="18" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1258,19 +1258,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{290E42D8-F80B-412C-AAD2-3573AA96BBDE}">
-  <dimension ref="A1:Q32"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00FC7CBB-7381-4674-9CEA-E2F5157726B5}">
+  <dimension ref="A1:Q33"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.125" customWidth="1"/>
-    <col min="2" max="5" width="12.625" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="13.875" customWidth="1"/>
-    <col min="8" max="10" width="12" customWidth="1"/>
-    <col min="11" max="11" width="12.625" customWidth="1"/>
-    <col min="12" max="15" width="12" customWidth="1"/>
-    <col min="16" max="16" width="12.625" customWidth="1"/>
-    <col min="17" max="17" width="13.75" customWidth="1"/>
+    <col min="1" max="1" width="9.375" customWidth="1"/>
+    <col min="2" max="5" width="7.875" customWidth="1"/>
+    <col min="6" max="6" width="7.5" customWidth="1"/>
+    <col min="7" max="7" width="8.625" customWidth="1"/>
+    <col min="8" max="10" width="7.5" customWidth="1"/>
+    <col min="11" max="11" width="7.875" customWidth="1"/>
+    <col min="12" max="15" width="7.5" customWidth="1"/>
+    <col min="16" max="16" width="7.875" customWidth="1"/>
+    <col min="17" max="17" width="8.25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -1423,696 +1423,696 @@
     </row>
     <row r="5" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="B5" s="6">
-        <v>104.5</v>
+        <v>92.9</v>
       </c>
       <c r="C5" s="6">
-        <v>95.7</v>
+        <v>90.9</v>
       </c>
       <c r="D5" s="6">
-        <v>104.5</v>
+        <v>93</v>
       </c>
       <c r="E5" s="6">
-        <v>91.6</v>
+        <v>85.3</v>
       </c>
       <c r="F5" s="7">
-        <v>-7.8</v>
+        <v>-4.8</v>
       </c>
       <c r="G5" s="7">
-        <v>-7.54</v>
+        <v>-5.0199999999999996</v>
       </c>
       <c r="H5" s="8">
-        <v>4.46</v>
-      </c>
-      <c r="I5" s="9">
-        <v>12</v>
+        <v>4</v>
+      </c>
+      <c r="I5" s="7">
+        <v>-10.3</v>
       </c>
       <c r="J5" s="9">
-        <v>30.7</v>
+        <v>18.100000000000001</v>
       </c>
       <c r="K5" s="8">
-        <v>40.520000000000003</v>
+        <v>44.52</v>
       </c>
       <c r="L5" s="9">
-        <v>10.6</v>
+        <v>11.2</v>
       </c>
       <c r="M5" s="8">
-        <v>4.46</v>
-      </c>
-      <c r="N5" s="9">
-        <v>12</v>
+        <v>4</v>
+      </c>
+      <c r="N5" s="7">
+        <v>-10.3</v>
       </c>
       <c r="O5" s="9">
-        <v>30.7</v>
+        <v>18.100000000000001</v>
       </c>
       <c r="P5" s="8">
-        <v>40.520000000000003</v>
+        <v>44.52</v>
       </c>
       <c r="Q5" s="9">
-        <v>10.6</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="6" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="11">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="B6" s="12">
-        <v>104</v>
+        <v>104.5</v>
       </c>
       <c r="C6" s="12">
-        <v>103.5</v>
+        <v>95.7</v>
       </c>
       <c r="D6" s="12">
-        <v>109.5</v>
+        <v>104.5</v>
       </c>
       <c r="E6" s="12">
-        <v>97.3</v>
+        <v>91.6</v>
       </c>
       <c r="F6" s="13">
-        <v>1</v>
+        <v>-7.8</v>
       </c>
       <c r="G6" s="13">
-        <v>0.98</v>
+        <v>-7.54</v>
       </c>
       <c r="H6" s="14">
-        <v>3.98</v>
-      </c>
-      <c r="I6" s="13">
-        <v>2.79</v>
-      </c>
-      <c r="J6" s="13">
-        <v>18.8</v>
+        <v>4.46</v>
+      </c>
+      <c r="I6" s="15">
+        <v>12</v>
+      </c>
+      <c r="J6" s="15">
+        <v>30.7</v>
       </c>
       <c r="K6" s="14">
-        <v>36.07</v>
-      </c>
-      <c r="L6" s="13">
-        <v>8.5299999999999994</v>
+        <v>40.520000000000003</v>
+      </c>
+      <c r="L6" s="15">
+        <v>10.6</v>
       </c>
       <c r="M6" s="14">
-        <v>3.98</v>
-      </c>
-      <c r="N6" s="13">
-        <v>2.79</v>
-      </c>
-      <c r="O6" s="13">
-        <v>18.8</v>
+        <v>4.46</v>
+      </c>
+      <c r="N6" s="15">
+        <v>12</v>
+      </c>
+      <c r="O6" s="15">
+        <v>30.7</v>
       </c>
       <c r="P6" s="14">
-        <v>36.07</v>
-      </c>
-      <c r="Q6" s="13">
-        <v>8.5299999999999994</v>
+        <v>40.520000000000003</v>
+      </c>
+      <c r="Q6" s="15">
+        <v>10.6</v>
       </c>
     </row>
     <row r="7" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="B7" s="6">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="C7" s="6">
-        <v>102.5</v>
+        <v>103.5</v>
       </c>
       <c r="D7" s="6">
-        <v>105.5</v>
+        <v>109.5</v>
       </c>
       <c r="E7" s="6">
-        <v>95</v>
+        <v>97.3</v>
       </c>
       <c r="F7" s="9">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G7" s="9">
-        <v>8.4700000000000006</v>
+        <v>0.98</v>
       </c>
       <c r="H7" s="8">
-        <v>3.87</v>
+        <v>3.98</v>
       </c>
       <c r="I7" s="9">
-        <v>2.59</v>
+        <v>2.79</v>
       </c>
       <c r="J7" s="9">
-        <v>18.100000000000001</v>
+        <v>18.8</v>
       </c>
       <c r="K7" s="8">
-        <v>32.08</v>
+        <v>36.07</v>
       </c>
       <c r="L7" s="9">
-        <v>7.38</v>
+        <v>8.5299999999999994</v>
       </c>
       <c r="M7" s="8">
-        <v>3.87</v>
+        <v>3.98</v>
       </c>
       <c r="N7" s="9">
-        <v>2.59</v>
+        <v>2.79</v>
       </c>
       <c r="O7" s="9">
-        <v>18.100000000000001</v>
+        <v>18.8</v>
       </c>
       <c r="P7" s="8">
-        <v>32.08</v>
+        <v>36.07</v>
       </c>
       <c r="Q7" s="9">
-        <v>7.38</v>
+        <v>8.5299999999999994</v>
       </c>
     </row>
     <row r="8" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="11">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="B8" s="12">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="C8" s="12">
-        <v>94.5</v>
+        <v>102.5</v>
       </c>
       <c r="D8" s="12">
-        <v>109</v>
+        <v>105.5</v>
       </c>
       <c r="E8" s="12">
-        <v>93.5</v>
+        <v>95</v>
       </c>
       <c r="F8" s="15">
-        <v>-12.5</v>
+        <v>8</v>
       </c>
       <c r="G8" s="15">
-        <v>-11.68</v>
+        <v>8.4700000000000006</v>
       </c>
       <c r="H8" s="14">
-        <v>3.78</v>
-      </c>
-      <c r="I8" s="13">
-        <v>5.83</v>
-      </c>
-      <c r="J8" s="13">
-        <v>8.64</v>
+        <v>3.87</v>
+      </c>
+      <c r="I8" s="15">
+        <v>2.59</v>
+      </c>
+      <c r="J8" s="15">
+        <v>18.100000000000001</v>
       </c>
       <c r="K8" s="14">
-        <v>28.21</v>
-      </c>
-      <c r="L8" s="13">
-        <v>6.06</v>
+        <v>32.08</v>
+      </c>
+      <c r="L8" s="15">
+        <v>7.38</v>
       </c>
       <c r="M8" s="14">
-        <v>3.78</v>
-      </c>
-      <c r="N8" s="13">
-        <v>5.83</v>
-      </c>
-      <c r="O8" s="13">
-        <v>8.64</v>
+        <v>3.87</v>
+      </c>
+      <c r="N8" s="15">
+        <v>2.59</v>
+      </c>
+      <c r="O8" s="15">
+        <v>18.100000000000001</v>
       </c>
       <c r="P8" s="14">
-        <v>28.21</v>
-      </c>
-      <c r="Q8" s="13">
-        <v>6.06</v>
+        <v>32.08</v>
+      </c>
+      <c r="Q8" s="15">
+        <v>7.38</v>
       </c>
     </row>
     <row r="9" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
-        <v>45839</v>
+        <v>45870</v>
       </c>
       <c r="B9" s="6">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C9" s="6">
-        <v>107</v>
+        <v>94.5</v>
       </c>
       <c r="D9" s="6">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="E9" s="6">
-        <v>103</v>
+        <v>93.5</v>
       </c>
       <c r="F9" s="7">
-        <v>-5</v>
+        <v>-12.5</v>
       </c>
       <c r="G9" s="7">
-        <v>-4.46</v>
+        <v>-11.68</v>
       </c>
       <c r="H9" s="8">
-        <v>3.57</v>
+        <v>3.78</v>
       </c>
       <c r="I9" s="9">
-        <v>6.81</v>
+        <v>5.83</v>
       </c>
       <c r="J9" s="9">
-        <v>0.76</v>
+        <v>8.64</v>
       </c>
       <c r="K9" s="8">
-        <v>24.43</v>
+        <v>28.21</v>
       </c>
       <c r="L9" s="9">
-        <v>5.67</v>
+        <v>6.06</v>
       </c>
       <c r="M9" s="8">
-        <v>3.57</v>
+        <v>3.78</v>
       </c>
       <c r="N9" s="9">
-        <v>6.81</v>
+        <v>5.83</v>
       </c>
       <c r="O9" s="9">
-        <v>0.76</v>
+        <v>8.64</v>
       </c>
       <c r="P9" s="8">
-        <v>24.43</v>
+        <v>28.21</v>
       </c>
       <c r="Q9" s="9">
-        <v>5.67</v>
+        <v>6.06</v>
       </c>
     </row>
     <row r="10" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="11">
-        <v>45809</v>
+        <v>45839</v>
       </c>
       <c r="B10" s="12">
-        <v>106.5</v>
+        <v>112</v>
       </c>
       <c r="C10" s="12">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="D10" s="12">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E10" s="12">
         <v>103</v>
       </c>
       <c r="F10" s="13">
-        <v>7</v>
+        <v>-5</v>
       </c>
       <c r="G10" s="13">
-        <v>6.67</v>
+        <v>-4.46</v>
       </c>
       <c r="H10" s="14">
-        <v>3.34</v>
+        <v>3.57</v>
       </c>
       <c r="I10" s="15">
-        <v>-4.6399999999999997</v>
-      </c>
-      <c r="J10" s="13">
-        <v>0.17</v>
+        <v>6.81</v>
+      </c>
+      <c r="J10" s="15">
+        <v>0.76</v>
       </c>
       <c r="K10" s="14">
-        <v>20.86</v>
-      </c>
-      <c r="L10" s="13">
-        <v>6.56</v>
+        <v>24.43</v>
+      </c>
+      <c r="L10" s="15">
+        <v>5.67</v>
       </c>
       <c r="M10" s="14">
-        <v>3.34</v>
+        <v>3.57</v>
       </c>
       <c r="N10" s="15">
-        <v>-4.6399999999999997</v>
-      </c>
-      <c r="O10" s="13">
-        <v>0.17</v>
+        <v>6.81</v>
+      </c>
+      <c r="O10" s="15">
+        <v>0.76</v>
       </c>
       <c r="P10" s="14">
-        <v>20.86</v>
-      </c>
-      <c r="Q10" s="13">
-        <v>6.56</v>
+        <v>24.43</v>
+      </c>
+      <c r="Q10" s="15">
+        <v>5.67</v>
       </c>
     </row>
     <row r="11" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
-        <v>45778</v>
+        <v>45809</v>
       </c>
       <c r="B11" s="6">
-        <v>108.5</v>
+        <v>106.5</v>
       </c>
       <c r="C11" s="6">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="D11" s="6">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="E11" s="6">
-        <v>100</v>
-      </c>
-      <c r="F11" s="7">
-        <v>-4.5</v>
-      </c>
-      <c r="G11" s="7">
-        <v>-4.1100000000000003</v>
+        <v>103</v>
+      </c>
+      <c r="F11" s="9">
+        <v>7</v>
+      </c>
+      <c r="G11" s="9">
+        <v>6.67</v>
       </c>
       <c r="H11" s="8">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="I11" s="7">
-        <v>-0.69</v>
-      </c>
-      <c r="J11" s="7">
-        <v>-0.1</v>
+        <v>-4.6399999999999997</v>
+      </c>
+      <c r="J11" s="9">
+        <v>0.17</v>
       </c>
       <c r="K11" s="8">
-        <v>17.52</v>
+        <v>20.86</v>
       </c>
       <c r="L11" s="9">
-        <v>7.87</v>
+        <v>6.56</v>
       </c>
       <c r="M11" s="8">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="N11" s="7">
-        <v>-0.69</v>
-      </c>
-      <c r="O11" s="7">
-        <v>-0.1</v>
+        <v>-4.6399999999999997</v>
+      </c>
+      <c r="O11" s="9">
+        <v>0.17</v>
       </c>
       <c r="P11" s="8">
-        <v>17.52</v>
+        <v>20.86</v>
       </c>
       <c r="Q11" s="9">
-        <v>7.87</v>
+        <v>6.56</v>
       </c>
     </row>
     <row r="12" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="11">
-        <v>45748</v>
+        <v>45778</v>
       </c>
       <c r="B12" s="12">
-        <v>123</v>
+        <v>108.5</v>
       </c>
       <c r="C12" s="12">
-        <v>109.5</v>
+        <v>105</v>
       </c>
       <c r="D12" s="12">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="E12" s="12">
-        <v>92.2</v>
-      </c>
-      <c r="F12" s="15">
-        <v>-10.5</v>
-      </c>
-      <c r="G12" s="15">
-        <v>-8.75</v>
+        <v>100</v>
+      </c>
+      <c r="F12" s="13">
+        <v>-4.5</v>
+      </c>
+      <c r="G12" s="13">
+        <v>-4.1100000000000003</v>
       </c>
       <c r="H12" s="14">
-        <v>3.53</v>
-      </c>
-      <c r="I12" s="15">
-        <v>-0.33</v>
+        <v>3.5</v>
+      </c>
+      <c r="I12" s="13">
+        <v>-0.69</v>
       </c>
       <c r="J12" s="13">
-        <v>5.95</v>
+        <v>-0.1</v>
       </c>
       <c r="K12" s="14">
-        <v>14.02</v>
-      </c>
-      <c r="L12" s="13">
-        <v>10.1</v>
+        <v>17.52</v>
+      </c>
+      <c r="L12" s="15">
+        <v>7.87</v>
       </c>
       <c r="M12" s="14">
-        <v>3.53</v>
-      </c>
-      <c r="N12" s="15">
-        <v>-0.33</v>
+        <v>3.5</v>
+      </c>
+      <c r="N12" s="13">
+        <v>-0.69</v>
       </c>
       <c r="O12" s="13">
-        <v>5.95</v>
+        <v>-0.1</v>
       </c>
       <c r="P12" s="14">
-        <v>14.02</v>
-      </c>
-      <c r="Q12" s="13">
-        <v>10.1</v>
+        <v>17.52</v>
+      </c>
+      <c r="Q12" s="15">
+        <v>7.87</v>
       </c>
     </row>
     <row r="13" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
-        <v>45717</v>
+        <v>45748</v>
       </c>
       <c r="B13" s="6">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="C13" s="6">
-        <v>120</v>
+        <v>109.5</v>
       </c>
       <c r="D13" s="6">
-        <v>133.5</v>
+        <v>123</v>
       </c>
       <c r="E13" s="6">
-        <v>120</v>
+        <v>92.2</v>
       </c>
       <c r="F13" s="7">
-        <v>-11</v>
+        <v>-10.5</v>
       </c>
       <c r="G13" s="7">
-        <v>-8.4</v>
+        <v>-8.75</v>
       </c>
       <c r="H13" s="8">
-        <v>3.54</v>
-      </c>
-      <c r="I13" s="9">
-        <v>6.24</v>
+        <v>3.53</v>
+      </c>
+      <c r="I13" s="7">
+        <v>-0.33</v>
       </c>
       <c r="J13" s="9">
-        <v>9.64</v>
+        <v>5.95</v>
       </c>
       <c r="K13" s="8">
-        <v>10.49</v>
+        <v>14.02</v>
       </c>
       <c r="L13" s="9">
-        <v>11.5</v>
+        <v>10.1</v>
       </c>
       <c r="M13" s="8">
-        <v>3.54</v>
-      </c>
-      <c r="N13" s="9">
-        <v>6.24</v>
+        <v>3.53</v>
+      </c>
+      <c r="N13" s="7">
+        <v>-0.33</v>
       </c>
       <c r="O13" s="9">
-        <v>9.64</v>
+        <v>5.95</v>
       </c>
       <c r="P13" s="8">
-        <v>10.49</v>
+        <v>14.02</v>
       </c>
       <c r="Q13" s="9">
-        <v>11.5</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="14" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="11">
-        <v>45689</v>
+        <v>45717</v>
       </c>
       <c r="B14" s="12">
-        <v>124.5</v>
+        <v>131</v>
       </c>
       <c r="C14" s="12">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="D14" s="12">
-        <v>144</v>
+        <v>133.5</v>
       </c>
       <c r="E14" s="12">
-        <v>122.5</v>
+        <v>120</v>
       </c>
       <c r="F14" s="13">
-        <v>6</v>
+        <v>-11</v>
       </c>
       <c r="G14" s="13">
-        <v>4.8</v>
+        <v>-8.4</v>
       </c>
       <c r="H14" s="14">
-        <v>3.33</v>
+        <v>3.54</v>
       </c>
       <c r="I14" s="15">
-        <v>-8.06</v>
-      </c>
-      <c r="J14" s="13">
-        <v>13.4</v>
+        <v>6.24</v>
+      </c>
+      <c r="J14" s="15">
+        <v>9.64</v>
       </c>
       <c r="K14" s="14">
-        <v>6.95</v>
-      </c>
-      <c r="L14" s="13">
-        <v>12.5</v>
+        <v>10.49</v>
+      </c>
+      <c r="L14" s="15">
+        <v>11.5</v>
       </c>
       <c r="M14" s="14">
-        <v>3.33</v>
+        <v>3.54</v>
       </c>
       <c r="N14" s="15">
-        <v>-8.06</v>
-      </c>
-      <c r="O14" s="13">
-        <v>13.4</v>
+        <v>6.24</v>
+      </c>
+      <c r="O14" s="15">
+        <v>9.64</v>
       </c>
       <c r="P14" s="14">
-        <v>6.95</v>
-      </c>
-      <c r="Q14" s="13">
-        <v>12.5</v>
+        <v>10.49</v>
+      </c>
+      <c r="Q14" s="15">
+        <v>11.5</v>
       </c>
     </row>
     <row r="15" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
-        <v>45658</v>
+        <v>45689</v>
       </c>
       <c r="B15" s="6">
-        <v>130</v>
+        <v>124.5</v>
       </c>
       <c r="C15" s="6">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="D15" s="6">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="E15" s="6">
-        <v>120</v>
-      </c>
-      <c r="F15" s="7">
-        <v>-4.5</v>
-      </c>
-      <c r="G15" s="7">
-        <v>-3.47</v>
+        <v>122.5</v>
+      </c>
+      <c r="F15" s="9">
+        <v>6</v>
+      </c>
+      <c r="G15" s="9">
+        <v>4.8</v>
       </c>
       <c r="H15" s="8">
-        <v>3.62</v>
-      </c>
-      <c r="I15" s="9">
-        <v>6.98</v>
+        <v>3.33</v>
+      </c>
+      <c r="I15" s="7">
+        <v>-8.06</v>
       </c>
       <c r="J15" s="9">
-        <v>11.7</v>
+        <v>13.4</v>
       </c>
       <c r="K15" s="8">
-        <v>3.62</v>
+        <v>6.95</v>
       </c>
       <c r="L15" s="9">
-        <v>11.7</v>
+        <v>12.5</v>
       </c>
       <c r="M15" s="8">
-        <v>3.62</v>
-      </c>
-      <c r="N15" s="9">
-        <v>6.98</v>
+        <v>3.33</v>
+      </c>
+      <c r="N15" s="7">
+        <v>-8.06</v>
       </c>
       <c r="O15" s="9">
-        <v>11.7</v>
+        <v>13.4</v>
       </c>
       <c r="P15" s="8">
-        <v>3.62</v>
+        <v>6.95</v>
       </c>
       <c r="Q15" s="9">
-        <v>11.7</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="16" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="11">
-        <v>45627</v>
+        <v>45658</v>
       </c>
       <c r="B16" s="12">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C16" s="12">
-        <v>129.5</v>
+        <v>125</v>
       </c>
       <c r="D16" s="12">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E16" s="12">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F16" s="13">
-        <v>28.5</v>
+        <v>-4.5</v>
       </c>
       <c r="G16" s="13">
-        <v>28.22</v>
+        <v>-3.47</v>
       </c>
       <c r="H16" s="14">
-        <v>3.39</v>
+        <v>3.62</v>
       </c>
       <c r="I16" s="15">
-        <v>-0.72</v>
+        <v>6.98</v>
       </c>
       <c r="J16" s="15">
-        <v>-16.399999999999999</v>
+        <v>11.7</v>
       </c>
       <c r="K16" s="14">
-        <v>40.03</v>
+        <v>3.62</v>
       </c>
       <c r="L16" s="15">
-        <v>-15.7</v>
+        <v>11.7</v>
       </c>
       <c r="M16" s="14">
-        <v>3.39</v>
+        <v>3.62</v>
       </c>
       <c r="N16" s="15">
-        <v>-0.72</v>
+        <v>6.98</v>
       </c>
       <c r="O16" s="15">
-        <v>-16.399999999999999</v>
+        <v>11.7</v>
       </c>
       <c r="P16" s="14">
-        <v>40.03</v>
+        <v>3.62</v>
       </c>
       <c r="Q16" s="15">
-        <v>-15.7</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="17" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
-        <v>45597</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F17" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G17" s="8" t="s">
-        <v>17</v>
+        <v>45627</v>
+      </c>
+      <c r="B17" s="6">
+        <v>129</v>
+      </c>
+      <c r="C17" s="6">
+        <v>129.5</v>
+      </c>
+      <c r="D17" s="6">
+        <v>135</v>
+      </c>
+      <c r="E17" s="6">
+        <v>119</v>
+      </c>
+      <c r="F17" s="9">
+        <v>28.5</v>
+      </c>
+      <c r="G17" s="9">
+        <v>28.22</v>
       </c>
       <c r="H17" s="8">
-        <v>3.41</v>
-      </c>
-      <c r="I17" s="9">
-        <v>1.76</v>
+        <v>3.39</v>
+      </c>
+      <c r="I17" s="7">
+        <v>-0.72</v>
       </c>
       <c r="J17" s="7">
-        <v>-17.8</v>
+        <v>-16.399999999999999</v>
       </c>
       <c r="K17" s="8">
-        <v>36.64</v>
+        <v>40.03</v>
       </c>
       <c r="L17" s="7">
-        <v>-15.6</v>
+        <v>-15.7</v>
       </c>
       <c r="M17" s="8">
-        <v>3.41</v>
-      </c>
-      <c r="N17" s="9">
-        <v>1.76</v>
+        <v>3.39</v>
+      </c>
+      <c r="N17" s="7">
+        <v>-0.72</v>
       </c>
       <c r="O17" s="7">
-        <v>-17.8</v>
+        <v>-16.399999999999999</v>
       </c>
       <c r="P17" s="8">
-        <v>36.64</v>
+        <v>40.03</v>
       </c>
       <c r="Q17" s="7">
-        <v>-15.6</v>
+        <v>-15.7</v>
       </c>
     </row>
     <row r="18" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="11">
-        <v>45566</v>
+        <v>45597</v>
       </c>
       <c r="B18" s="12" t="s">
         <v>17</v>
@@ -2133,39 +2133,39 @@
         <v>17</v>
       </c>
       <c r="H18" s="14">
-        <v>3.35</v>
-      </c>
-      <c r="I18" s="13">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="J18" s="15">
-        <v>-17.600000000000001</v>
+        <v>3.41</v>
+      </c>
+      <c r="I18" s="15">
+        <v>1.76</v>
+      </c>
+      <c r="J18" s="13">
+        <v>-17.8</v>
       </c>
       <c r="K18" s="14">
-        <v>33.229999999999997</v>
-      </c>
-      <c r="L18" s="15">
-        <v>-15.4</v>
+        <v>36.64</v>
+      </c>
+      <c r="L18" s="13">
+        <v>-15.6</v>
       </c>
       <c r="M18" s="14">
-        <v>3.35</v>
-      </c>
-      <c r="N18" s="13">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="O18" s="15">
-        <v>-17.600000000000001</v>
+        <v>3.41</v>
+      </c>
+      <c r="N18" s="15">
+        <v>1.76</v>
+      </c>
+      <c r="O18" s="13">
+        <v>-17.8</v>
       </c>
       <c r="P18" s="14">
-        <v>33.229999999999997</v>
-      </c>
-      <c r="Q18" s="15">
-        <v>-15.4</v>
+        <v>36.64</v>
+      </c>
+      <c r="Q18" s="13">
+        <v>-15.6</v>
       </c>
     </row>
     <row r="19" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
-        <v>45536</v>
+        <v>45566</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>17</v>
@@ -2186,39 +2186,39 @@
         <v>17</v>
       </c>
       <c r="H19" s="8">
-        <v>3.28</v>
-      </c>
-      <c r="I19" s="7">
-        <v>-5.62</v>
+        <v>3.35</v>
+      </c>
+      <c r="I19" s="9">
+        <v>2.2000000000000002</v>
       </c>
       <c r="J19" s="7">
-        <v>-16.8</v>
+        <v>-17.600000000000001</v>
       </c>
       <c r="K19" s="8">
-        <v>29.88</v>
+        <v>33.229999999999997</v>
       </c>
       <c r="L19" s="7">
-        <v>-15.2</v>
+        <v>-15.4</v>
       </c>
       <c r="M19" s="8">
-        <v>3.28</v>
-      </c>
-      <c r="N19" s="7">
-        <v>-5.62</v>
+        <v>3.35</v>
+      </c>
+      <c r="N19" s="9">
+        <v>2.2000000000000002</v>
       </c>
       <c r="O19" s="7">
-        <v>-16.8</v>
+        <v>-17.600000000000001</v>
       </c>
       <c r="P19" s="8">
-        <v>29.88</v>
+        <v>33.229999999999997</v>
       </c>
       <c r="Q19" s="7">
-        <v>-15.2</v>
+        <v>-15.4</v>
       </c>
     </row>
     <row r="20" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="11">
-        <v>45505</v>
+        <v>45536</v>
       </c>
       <c r="B20" s="12" t="s">
         <v>17</v>
@@ -2239,39 +2239,39 @@
         <v>17</v>
       </c>
       <c r="H20" s="14">
-        <v>3.48</v>
-      </c>
-      <c r="I20" s="15">
-        <v>-1.83</v>
-      </c>
-      <c r="J20" s="15">
-        <v>-14</v>
+        <v>3.28</v>
+      </c>
+      <c r="I20" s="13">
+        <v>-5.62</v>
+      </c>
+      <c r="J20" s="13">
+        <v>-16.8</v>
       </c>
       <c r="K20" s="14">
-        <v>26.6</v>
-      </c>
-      <c r="L20" s="15">
-        <v>-15</v>
+        <v>29.88</v>
+      </c>
+      <c r="L20" s="13">
+        <v>-15.2</v>
       </c>
       <c r="M20" s="14">
-        <v>3.48</v>
-      </c>
-      <c r="N20" s="15">
-        <v>-1.83</v>
-      </c>
-      <c r="O20" s="15">
-        <v>-14</v>
+        <v>3.28</v>
+      </c>
+      <c r="N20" s="13">
+        <v>-5.62</v>
+      </c>
+      <c r="O20" s="13">
+        <v>-16.8</v>
       </c>
       <c r="P20" s="14">
-        <v>26.6</v>
-      </c>
-      <c r="Q20" s="15">
-        <v>-15</v>
+        <v>29.88</v>
+      </c>
+      <c r="Q20" s="13">
+        <v>-15.2</v>
       </c>
     </row>
     <row r="21" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
-        <v>45474</v>
+        <v>45505</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>17</v>
@@ -2292,39 +2292,39 @@
         <v>17</v>
       </c>
       <c r="H21" s="8">
-        <v>3.54</v>
-      </c>
-      <c r="I21" s="9">
-        <v>6.18</v>
+        <v>3.48</v>
+      </c>
+      <c r="I21" s="7">
+        <v>-1.83</v>
       </c>
       <c r="J21" s="7">
-        <v>-12.1</v>
+        <v>-14</v>
       </c>
       <c r="K21" s="8">
-        <v>23.12</v>
+        <v>26.6</v>
       </c>
       <c r="L21" s="7">
-        <v>-15.1</v>
+        <v>-15</v>
       </c>
       <c r="M21" s="8">
-        <v>3.54</v>
-      </c>
-      <c r="N21" s="9">
-        <v>6.18</v>
+        <v>3.48</v>
+      </c>
+      <c r="N21" s="7">
+        <v>-1.83</v>
       </c>
       <c r="O21" s="7">
-        <v>-12.1</v>
+        <v>-14</v>
       </c>
       <c r="P21" s="8">
-        <v>23.12</v>
+        <v>26.6</v>
       </c>
       <c r="Q21" s="7">
-        <v>-15.1</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="22" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="11">
-        <v>45444</v>
+        <v>45474</v>
       </c>
       <c r="B22" s="12" t="s">
         <v>17</v>
@@ -2345,39 +2345,39 @@
         <v>17</v>
       </c>
       <c r="H22" s="14">
-        <v>3.33</v>
+        <v>3.54</v>
       </c>
       <c r="I22" s="15">
-        <v>-4.91</v>
-      </c>
-      <c r="J22" s="15">
-        <v>-9.4600000000000009</v>
+        <v>6.18</v>
+      </c>
+      <c r="J22" s="13">
+        <v>-12.1</v>
       </c>
       <c r="K22" s="14">
-        <v>19.579999999999998</v>
-      </c>
-      <c r="L22" s="15">
-        <v>-15.6</v>
+        <v>23.12</v>
+      </c>
+      <c r="L22" s="13">
+        <v>-15.1</v>
       </c>
       <c r="M22" s="14">
-        <v>3.33</v>
+        <v>3.54</v>
       </c>
       <c r="N22" s="15">
-        <v>-4.91</v>
-      </c>
-      <c r="O22" s="15">
-        <v>-9.4600000000000009</v>
+        <v>6.18</v>
+      </c>
+      <c r="O22" s="13">
+        <v>-12.1</v>
       </c>
       <c r="P22" s="14">
-        <v>19.579999999999998</v>
-      </c>
-      <c r="Q22" s="15">
-        <v>-15.6</v>
+        <v>23.12</v>
+      </c>
+      <c r="Q22" s="13">
+        <v>-15.1</v>
       </c>
     </row>
     <row r="23" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
-        <v>45413</v>
+        <v>45444</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>17</v>
@@ -2398,39 +2398,39 @@
         <v>17</v>
       </c>
       <c r="H23" s="8">
-        <v>3.51</v>
-      </c>
-      <c r="I23" s="9">
-        <v>5.33</v>
+        <v>3.33</v>
+      </c>
+      <c r="I23" s="7">
+        <v>-4.91</v>
       </c>
       <c r="J23" s="7">
-        <v>-10.1</v>
+        <v>-9.4600000000000009</v>
       </c>
       <c r="K23" s="8">
-        <v>16.239999999999998</v>
+        <v>19.579999999999998</v>
       </c>
       <c r="L23" s="7">
-        <v>-16.8</v>
+        <v>-15.6</v>
       </c>
       <c r="M23" s="8">
-        <v>3.51</v>
-      </c>
-      <c r="N23" s="9">
-        <v>5.33</v>
+        <v>3.33</v>
+      </c>
+      <c r="N23" s="7">
+        <v>-4.91</v>
       </c>
       <c r="O23" s="7">
-        <v>-10.1</v>
+        <v>-9.4600000000000009</v>
       </c>
       <c r="P23" s="8">
-        <v>16.239999999999998</v>
+        <v>19.579999999999998</v>
       </c>
       <c r="Q23" s="7">
-        <v>-16.8</v>
+        <v>-15.6</v>
       </c>
     </row>
     <row r="24" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="11">
-        <v>45383</v>
+        <v>45413</v>
       </c>
       <c r="B24" s="12" t="s">
         <v>17</v>
@@ -2451,39 +2451,39 @@
         <v>17</v>
       </c>
       <c r="H24" s="14">
-        <v>3.33</v>
-      </c>
-      <c r="I24" s="13">
-        <v>3.13</v>
-      </c>
-      <c r="J24" s="15">
-        <v>-16</v>
+        <v>3.51</v>
+      </c>
+      <c r="I24" s="15">
+        <v>5.33</v>
+      </c>
+      <c r="J24" s="13">
+        <v>-10.1</v>
       </c>
       <c r="K24" s="14">
-        <v>12.74</v>
-      </c>
-      <c r="L24" s="15">
-        <v>-18.399999999999999</v>
+        <v>16.239999999999998</v>
+      </c>
+      <c r="L24" s="13">
+        <v>-16.8</v>
       </c>
       <c r="M24" s="14">
-        <v>3.33</v>
-      </c>
-      <c r="N24" s="13">
-        <v>3.13</v>
-      </c>
-      <c r="O24" s="15">
-        <v>-16</v>
+        <v>3.51</v>
+      </c>
+      <c r="N24" s="15">
+        <v>5.33</v>
+      </c>
+      <c r="O24" s="13">
+        <v>-10.1</v>
       </c>
       <c r="P24" s="14">
-        <v>12.74</v>
-      </c>
-      <c r="Q24" s="15">
-        <v>-18.399999999999999</v>
+        <v>16.239999999999998</v>
+      </c>
+      <c r="Q24" s="13">
+        <v>-16.8</v>
       </c>
     </row>
     <row r="25" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
-        <v>45352</v>
+        <v>45383</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>17</v>
@@ -2504,39 +2504,39 @@
         <v>17</v>
       </c>
       <c r="H25" s="8">
-        <v>3.23</v>
+        <v>3.33</v>
       </c>
       <c r="I25" s="9">
-        <v>9.89</v>
+        <v>3.13</v>
       </c>
       <c r="J25" s="7">
-        <v>-20.8</v>
+        <v>-16</v>
       </c>
       <c r="K25" s="8">
-        <v>9.41</v>
+        <v>12.74</v>
       </c>
       <c r="L25" s="7">
-        <v>-19.3</v>
+        <v>-18.399999999999999</v>
       </c>
       <c r="M25" s="8">
-        <v>3.23</v>
+        <v>3.33</v>
       </c>
       <c r="N25" s="9">
-        <v>9.89</v>
+        <v>3.13</v>
       </c>
       <c r="O25" s="7">
-        <v>-20.8</v>
+        <v>-16</v>
       </c>
       <c r="P25" s="8">
-        <v>9.41</v>
+        <v>12.74</v>
       </c>
       <c r="Q25" s="7">
-        <v>-19.3</v>
+        <v>-18.399999999999999</v>
       </c>
     </row>
     <row r="26" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="11">
-        <v>45323</v>
+        <v>45352</v>
       </c>
       <c r="B26" s="12" t="s">
         <v>17</v>
@@ -2557,39 +2557,39 @@
         <v>17</v>
       </c>
       <c r="H26" s="14">
-        <v>2.94</v>
+        <v>3.23</v>
       </c>
       <c r="I26" s="15">
-        <v>-9.44</v>
-      </c>
-      <c r="J26" s="15">
-        <v>-20.7</v>
+        <v>9.89</v>
+      </c>
+      <c r="J26" s="13">
+        <v>-20.8</v>
       </c>
       <c r="K26" s="14">
-        <v>6.18</v>
-      </c>
-      <c r="L26" s="15">
-        <v>-18.5</v>
+        <v>9.41</v>
+      </c>
+      <c r="L26" s="13">
+        <v>-19.3</v>
       </c>
       <c r="M26" s="14">
-        <v>2.94</v>
+        <v>3.23</v>
       </c>
       <c r="N26" s="15">
-        <v>-9.44</v>
-      </c>
-      <c r="O26" s="15">
-        <v>-20.7</v>
+        <v>9.89</v>
+      </c>
+      <c r="O26" s="13">
+        <v>-20.8</v>
       </c>
       <c r="P26" s="14">
-        <v>6.18</v>
-      </c>
-      <c r="Q26" s="15">
-        <v>-18.5</v>
+        <v>9.41</v>
+      </c>
+      <c r="Q26" s="13">
+        <v>-19.3</v>
       </c>
     </row>
     <row r="27" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
-        <v>45292</v>
+        <v>45323</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>17</v>
@@ -2610,39 +2610,39 @@
         <v>17</v>
       </c>
       <c r="H27" s="8">
-        <v>3.24</v>
+        <v>2.94</v>
       </c>
       <c r="I27" s="7">
-        <v>-19.899999999999999</v>
+        <v>-9.44</v>
       </c>
       <c r="J27" s="7">
-        <v>-16.399999999999999</v>
+        <v>-20.7</v>
       </c>
       <c r="K27" s="8">
-        <v>3.24</v>
+        <v>6.18</v>
       </c>
       <c r="L27" s="7">
-        <v>-16.399999999999999</v>
+        <v>-18.5</v>
       </c>
       <c r="M27" s="8">
-        <v>3.24</v>
+        <v>2.94</v>
       </c>
       <c r="N27" s="7">
-        <v>-19.899999999999999</v>
+        <v>-9.44</v>
       </c>
       <c r="O27" s="7">
-        <v>-16.399999999999999</v>
+        <v>-20.7</v>
       </c>
       <c r="P27" s="8">
-        <v>3.24</v>
+        <v>6.18</v>
       </c>
       <c r="Q27" s="7">
-        <v>-16.399999999999999</v>
+        <v>-18.5</v>
       </c>
     </row>
     <row r="28" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="11">
-        <v>45261</v>
+        <v>45292</v>
       </c>
       <c r="B28" s="12" t="s">
         <v>17</v>
@@ -2663,39 +2663,39 @@
         <v>17</v>
       </c>
       <c r="H28" s="14">
-        <v>4.05</v>
-      </c>
-      <c r="I28" s="15">
-        <v>-2.4300000000000002</v>
-      </c>
-      <c r="J28" s="15">
-        <v>-0.33</v>
+        <v>3.24</v>
+      </c>
+      <c r="I28" s="13">
+        <v>-19.899999999999999</v>
+      </c>
+      <c r="J28" s="13">
+        <v>-16.399999999999999</v>
       </c>
       <c r="K28" s="14">
-        <v>47.49</v>
-      </c>
-      <c r="L28" s="15">
-        <v>-6.19</v>
+        <v>3.24</v>
+      </c>
+      <c r="L28" s="13">
+        <v>-16.399999999999999</v>
       </c>
       <c r="M28" s="14">
-        <v>4.05</v>
-      </c>
-      <c r="N28" s="15">
-        <v>-2.4300000000000002</v>
-      </c>
-      <c r="O28" s="15">
-        <v>-0.33</v>
+        <v>3.24</v>
+      </c>
+      <c r="N28" s="13">
+        <v>-19.899999999999999</v>
+      </c>
+      <c r="O28" s="13">
+        <v>-16.399999999999999</v>
       </c>
       <c r="P28" s="14">
-        <v>47.49</v>
-      </c>
-      <c r="Q28" s="15">
-        <v>-6.19</v>
+        <v>3.24</v>
+      </c>
+      <c r="Q28" s="13">
+        <v>-16.399999999999999</v>
       </c>
     </row>
     <row r="29" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
-        <v>45231</v>
+        <v>45261</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>17</v>
@@ -2716,39 +2716,39 @@
         <v>17</v>
       </c>
       <c r="H29" s="8">
-        <v>4.1500000000000004</v>
-      </c>
-      <c r="I29" s="9">
-        <v>2.1</v>
+        <v>4.05</v>
+      </c>
+      <c r="I29" s="7">
+        <v>-2.4300000000000002</v>
       </c>
       <c r="J29" s="7">
-        <v>-5.1100000000000003</v>
+        <v>-0.33</v>
       </c>
       <c r="K29" s="8">
-        <v>43.43</v>
+        <v>47.49</v>
       </c>
       <c r="L29" s="7">
-        <v>-6.7</v>
+        <v>-6.19</v>
       </c>
       <c r="M29" s="8">
-        <v>4.1500000000000004</v>
-      </c>
-      <c r="N29" s="9">
-        <v>2.1</v>
+        <v>4.05</v>
+      </c>
+      <c r="N29" s="7">
+        <v>-2.4300000000000002</v>
       </c>
       <c r="O29" s="7">
-        <v>-5.1100000000000003</v>
+        <v>-0.33</v>
       </c>
       <c r="P29" s="8">
-        <v>43.43</v>
+        <v>47.49</v>
       </c>
       <c r="Q29" s="7">
-        <v>-6.7</v>
+        <v>-6.19</v>
       </c>
     </row>
     <row r="30" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11">
-        <v>45200</v>
+        <v>45231</v>
       </c>
       <c r="B30" s="12" t="s">
         <v>17</v>
@@ -2769,39 +2769,39 @@
         <v>17</v>
       </c>
       <c r="H30" s="14">
-        <v>4.07</v>
-      </c>
-      <c r="I30" s="13">
-        <v>3.2</v>
-      </c>
-      <c r="J30" s="15">
-        <v>-7.53</v>
+        <v>4.1500000000000004</v>
+      </c>
+      <c r="I30" s="15">
+        <v>2.1</v>
+      </c>
+      <c r="J30" s="13">
+        <v>-5.1100000000000003</v>
       </c>
       <c r="K30" s="14">
-        <v>39.28</v>
-      </c>
-      <c r="L30" s="15">
-        <v>-6.86</v>
+        <v>43.43</v>
+      </c>
+      <c r="L30" s="13">
+        <v>-6.7</v>
       </c>
       <c r="M30" s="14">
-        <v>4.07</v>
-      </c>
-      <c r="N30" s="13">
-        <v>3.2</v>
-      </c>
-      <c r="O30" s="15">
-        <v>-7.53</v>
+        <v>4.1500000000000004</v>
+      </c>
+      <c r="N30" s="15">
+        <v>2.1</v>
+      </c>
+      <c r="O30" s="13">
+        <v>-5.1100000000000003</v>
       </c>
       <c r="P30" s="14">
-        <v>39.28</v>
-      </c>
-      <c r="Q30" s="15">
-        <v>-6.86</v>
+        <v>43.43</v>
+      </c>
+      <c r="Q30" s="13">
+        <v>-6.7</v>
       </c>
     </row>
     <row r="31" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5">
-        <v>45170</v>
+        <v>45200</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>17</v>
@@ -2822,86 +2822,139 @@
         <v>17</v>
       </c>
       <c r="H31" s="8">
-        <v>3.94</v>
-      </c>
-      <c r="I31" s="7">
-        <v>-2.44</v>
+        <v>4.07</v>
+      </c>
+      <c r="I31" s="9">
+        <v>3.2</v>
       </c>
       <c r="J31" s="7">
         <v>-7.53</v>
       </c>
       <c r="K31" s="8">
-        <v>35.21</v>
+        <v>39.28</v>
       </c>
       <c r="L31" s="7">
-        <v>-6.78</v>
+        <v>-6.86</v>
       </c>
       <c r="M31" s="8">
-        <v>3.94</v>
-      </c>
-      <c r="N31" s="7">
-        <v>-2.44</v>
+        <v>4.07</v>
+      </c>
+      <c r="N31" s="9">
+        <v>3.2</v>
       </c>
       <c r="O31" s="7">
         <v>-7.53</v>
       </c>
       <c r="P31" s="8">
-        <v>35.21</v>
+        <v>39.28</v>
       </c>
       <c r="Q31" s="7">
-        <v>-6.78</v>
+        <v>-6.86</v>
       </c>
     </row>
     <row r="32" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="11">
+        <v>45170</v>
+      </c>
+      <c r="B32" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C32" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D32" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E32" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="F32" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="G32" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="H32" s="14">
+        <v>3.94</v>
+      </c>
+      <c r="I32" s="13">
+        <v>-2.44</v>
+      </c>
+      <c r="J32" s="13">
+        <v>-7.53</v>
+      </c>
+      <c r="K32" s="14">
+        <v>35.21</v>
+      </c>
+      <c r="L32" s="13">
+        <v>-6.78</v>
+      </c>
+      <c r="M32" s="14">
+        <v>3.94</v>
+      </c>
+      <c r="N32" s="13">
+        <v>-2.44</v>
+      </c>
+      <c r="O32" s="13">
+        <v>-7.53</v>
+      </c>
+      <c r="P32" s="14">
+        <v>35.21</v>
+      </c>
+      <c r="Q32" s="13">
+        <v>-6.78</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="5">
         <v>45139</v>
       </c>
-      <c r="B32" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="C32" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="D32" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E32" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="F32" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="G32" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="H32" s="14">
+      <c r="B33" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F33" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G33" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="H33" s="8">
         <v>4.04</v>
       </c>
-      <c r="I32" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="J32" s="15">
+      <c r="I33" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="J33" s="7">
         <v>-5.43</v>
       </c>
-      <c r="K32" s="14">
+      <c r="K33" s="8">
         <v>31.27</v>
       </c>
-      <c r="L32" s="15">
+      <c r="L33" s="7">
         <v>-6.69</v>
       </c>
-      <c r="M32" s="14">
+      <c r="M33" s="8">
         <v>4.04</v>
       </c>
-      <c r="N32" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="O32" s="15">
+      <c r="N33" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="O33" s="7">
         <v>-5.43</v>
       </c>
-      <c r="P32" s="14">
+      <c r="P33" s="8">
         <v>31.27</v>
       </c>
-      <c r="Q32" s="15">
+      <c r="Q33" s="7">
         <v>-6.69</v>
       </c>
     </row>
